--- a/data/historico.xlsx
+++ b/data/historico.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I130"/>
+  <dimension ref="A1:I133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5440,6 +5440,123 @@
         </is>
       </c>
     </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46308.83690972222</v>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Headset Razer BlackShark V2 X</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>KaBuM!</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>359.99</v>
+      </c>
+      <c r="E131" t="n">
+        <v>365</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0</v>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>🎯 Meta atingida</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>JSON-LD</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>https://www.kabum.com.br/produto/128544/headset-gamer-razer-blackshark-v2-x-drivers-50mm-microfone-cardioide-surround-7-1-3-5-mm-preto-rz04-03240100</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46308.83696759259</v>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Celular Samsung Galaxy S26 Ultra 5G, 256GB, 12GB RAM,...</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>6749</v>
+      </c>
+      <c r="E132" t="n">
+        <v>6930</v>
+      </c>
+      <c r="F132" t="n">
+        <v>-2.49</v>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>🎯 Meta atingida</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>https://www.amazon.com.br/Celular-Samsung-Galaxy-C%C3%A2mera-Qu%C3%A1drupla/dp/B0GKQTTCMM/ref=sr_1_4?dib=eyJ2IjoiMSJ9.vPSAC4pNHsg0gllOYcZZ8Zkuzt1yNFkcu2X_tMKNiB9rdWwRyMCyVdh7lIeGlIHbKGdOoSLb6CAEo6A0AWgUuJ5IDOBQnYIhJuKQIWiglZfC3TGNEtwYhpMbu9fmF_wYEO-1Pt0fkMDUvTsUCjUBwIufenBKSPtE_9cdDjA4VsoXwdr-kj1LcZ_vCrGSFXlJYsNqR0uebzA6iCMCyWThWzrY70kgLxkwEpRE4rcIPLfZgVaLeu5MUIsc7pCofVL9OhMLV12HiXnrT29hmssmRJvl-Y-s9199svaXSJwe6n8.GwDLQZm0nNpcnU0WPMNQqNDpKt7OHcqA_PyQxLi-A10&amp;dib_tag=se&amp;keywords=s26+ultra&amp;qid=1791500311&amp;sr=8-4&amp;ufe=app_do%3Aamzn1.fos.9e6a115c-05b9-4b96-8e1c-b1f9ce2ac1a6</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46308.83700231482</v>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Pore Refiner Creamy Skincare 70 Pads com Ácido Salicílico</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>132.04</v>
+      </c>
+      <c r="E133" t="n">
+        <v>140</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0</v>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>🎯 Meta atingida</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>https://www.amazon.com.br/Pore-Refiner-70-Pads-Salic%C3%ADlico/dp/B0HF61NDMW/ref=sr_1_6?dib=eyJ2IjoiMSJ9.uk1ZaTmLSkCjr1WlUdPnIzLaofEGDgJh9R7zYgwkefy9LuyQiFzUUu0aJIX1BYlx5-wRmSwJSUBKJnX-zzS0X0-VmfHtQQ82JcgAgtGQVEnj9-HHDeyGf3d1rYulXi7i_Ow8QIWh3kQqL7Ll0TijZfSoZQDQadHr_-rf6DfesXMmMibB6sDX6vWc2RnP-foaqCDGyT4duklJcGFpv1u51qTNZl50udCB94NihMSqwrPPI0LzQRiYV6gMXcGuIyLA-BMEaK8C7Ww9vfUFU3IpgOYQ1941MisZvR5CXyW4ppQ.78jHfHg1CNr1xN0-5kzhzBvDSAbiluwmUGIf3gB8a_0&amp;dib_tag=se&amp;keywords=creamy+pore+refiner&amp;qid=1791501119&amp;sr=8-6&amp;ufe=app_do%3Aamzn1.fos.6a09f7ec-d911-4889-ad70-de8dd83c8a74</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/historico.xlsx
+++ b/data/historico.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I133"/>
+  <dimension ref="A1:I157"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5175,7 +5175,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Pore Refiner Creamy Skincare 70 Pads com Ácido Salicílico</t>
+          <t>Creme Skincare com Ácido Salicílico | Creamy</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -5290,7 +5290,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Pore Refiner Creamy Skincare 70 Pads com Ácido Salicílico</t>
+          <t>Creme Skincare com Ácido Salicílico | Creamy</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -5407,7 +5407,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Pore Refiner Creamy Skincare 70 Pads com Ácido Salicílico</t>
+          <t>Creme Skincare com Ácido Salicílico | Creamy</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -5524,7 +5524,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Pore Refiner Creamy Skincare 70 Pads com Ácido Salicílico</t>
+          <t>Creme Skincare com Ácido Salicílico | Creamy</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -5554,6 +5554,910 @@
       <c r="I133" t="inlineStr">
         <is>
           <t>https://www.amazon.com.br/Pore-Refiner-70-Pads-Salic%C3%ADlico/dp/B0HF61NDMW/ref=sr_1_6?dib=eyJ2IjoiMSJ9.uk1ZaTmLSkCjr1WlUdPnIzLaofEGDgJh9R7zYgwkefy9LuyQiFzUUu0aJIX1BYlx5-wRmSwJSUBKJnX-zzS0X0-VmfHtQQ82JcgAgtGQVEnj9-HHDeyGf3d1rYulXi7i_Ow8QIWh3kQqL7Ll0TijZfSoZQDQadHr_-rf6DfesXMmMibB6sDX6vWc2RnP-foaqCDGyT4duklJcGFpv1u51qTNZl50udCB94NihMSqwrPPI0LzQRiYV6gMXcGuIyLA-BMEaK8C7Ww9vfUFU3IpgOYQ1941MisZvR5CXyW4ppQ.78jHfHg1CNr1xN0-5kzhzBvDSAbiluwmUGIf3gB8a_0&amp;dib_tag=se&amp;keywords=creamy+pore+refiner&amp;qid=1791501119&amp;sr=8-6&amp;ufe=app_do%3Aamzn1.fos.6a09f7ec-d911-4889-ad70-de8dd83c8a74</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46309.89174768519</v>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Headset Razer BlackShark V2 X</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>KaBuM!</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>359.99</v>
+      </c>
+      <c r="E134" t="n">
+        <v>365</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0</v>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>🎯 Meta atingida</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>JSON-LD</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>https://www.kabum.com.br/produto/128544/headset-gamer-razer-blackshark-v2-x-drivers-50mm-microfone-cardioide-surround-7-1-3-5-mm-preto-rz04-03240100</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46309.89179398148</v>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Creme Skincare com Ácido Salicílico | Creamy</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>132.04</v>
+      </c>
+      <c r="E135" t="n">
+        <v>100</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0</v>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>😐 Sem queda</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>https://www.amazon.com.br/Pore-Refiner-70-Pads-Salic%C3%ADlico/dp/B0HF61NDMW/ref=sr_1_6?dib=eyJ2IjoiMSJ9.uk1ZaTmLSkCjr1WlUdPnIzLaofEGDgJh9R7zYgwkefy9LuyQiFzUUu0aJIX1BYlx5-wRmSwJSUBKJnX-zzS0X0-VmfHtQQ82JcgAgtGQVEnj9-HHDeyGf3d1rYulXi7i_Ow8QIWh3kQqL7Ll0TijZfSoZQDQadHr_-rf6DfesXMmMibB6sDX6vWc2RnP-foaqCDGyT4duklJcGFpv1u51qTNZl50udCB94NihMSqwrPPI0LzQRiYV6gMXcGuIyLA-BMEaK8C7Ww9vfUFU3IpgOYQ1941MisZvR5CXyW4ppQ.78jHfHg1CNr1xN0-5kzhzBvDSAbiluwmUGIf3gB8a_0&amp;dib_tag=se&amp;keywords=creamy+pore+refiner&amp;qid=1791501119&amp;sr=8-6&amp;ufe=app_do%3Aamzn1.fos.6a09f7ec-d911-4889-ad70-de8dd83c8a74</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46309.89193287037</v>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Celular Samsung Galaxy S26 Ultra 5G, 256GB, 12GB RAM,...</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Mercado Livre</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr"/>
+      <c r="E136" t="n">
+        <v>6800</v>
+      </c>
+      <c r="F136" t="inlineStr"/>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>❌ Erro</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr"/>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>https://www.mercadolivre.com.br/celular-samsung-galaxy-s26-ultra-5g-256gb-12gb-ram-camera-quadrupla-tela-grande-de-69-violeta/p/MLB65503990</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46309.89261574074</v>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Headset Razer BlackShark V2 X</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>KaBuM!</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>359.99</v>
+      </c>
+      <c r="E137" t="n">
+        <v>365</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0</v>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>🎯 Meta atingida</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>JSON-LD</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>https://www.kabum.com.br/produto/128544/headset-gamer-razer-blackshark-v2-x-drivers-50mm-microfone-cardioide-surround-7-1-3-5-mm-preto-rz04-03240100</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46309.89268518519</v>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Creme Skincare com Ácido Salicílico | Creamy</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>132.04</v>
+      </c>
+      <c r="E138" t="n">
+        <v>100</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0</v>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>😐 Sem queda</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>https://www.amazon.com.br/Pore-Refiner-70-Pads-Salic%C3%ADlico/dp/B0HF61NDMW/ref=sr_1_6?dib=eyJ2IjoiMSJ9.uk1ZaTmLSkCjr1WlUdPnIzLaofEGDgJh9R7zYgwkefy9LuyQiFzUUu0aJIX1BYlx5-wRmSwJSUBKJnX-zzS0X0-VmfHtQQ82JcgAgtGQVEnj9-HHDeyGf3d1rYulXi7i_Ow8QIWh3kQqL7Ll0TijZfSoZQDQadHr_-rf6DfesXMmMibB6sDX6vWc2RnP-foaqCDGyT4duklJcGFpv1u51qTNZl50udCB94NihMSqwrPPI0LzQRiYV6gMXcGuIyLA-BMEaK8C7Ww9vfUFU3IpgOYQ1941MisZvR5CXyW4ppQ.78jHfHg1CNr1xN0-5kzhzBvDSAbiluwmUGIf3gB8a_0&amp;dib_tag=se&amp;keywords=creamy+pore+refiner&amp;qid=1791501119&amp;sr=8-6&amp;ufe=app_do%3Aamzn1.fos.6a09f7ec-d911-4889-ad70-de8dd83c8a74</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46309.89275462963</v>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Celular Samsung Galaxy S26 Ultra 5G, 256GB, 12GB RAM,...</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Mercado Livre</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>7498.89</v>
+      </c>
+      <c r="E139" t="n">
+        <v>6800</v>
+      </c>
+      <c r="F139" t="n">
+        <v>11.11</v>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>📈 Subiu</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>JSON-LD</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>https://www.mercadolivre.com.br/celular-samsung-galaxy-s26-ultra-5g-256gb-12gb-ram-camera-quadrupla-tela-grande-de-69-violeta/p/MLB65503990</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46309.89383101852</v>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Headset Razer BlackShark V2 X</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>KaBuM!</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>359.99</v>
+      </c>
+      <c r="E140" t="n">
+        <v>365</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0</v>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>🎯 Meta atingida</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>JSON-LD</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>https://www.kabum.com.br/produto/128544/headset-gamer-razer-blackshark-v2-x-drivers-50mm-microfone-cardioide-surround-7-1-3-5-mm-preto-rz04-03240100</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46309.89391203703</v>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Creme Skincare com Ácido Salicílico | Creamy</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>132.04</v>
+      </c>
+      <c r="E141" t="n">
+        <v>140</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0</v>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>🎯 Meta atingida</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>https://www.amazon.com.br/Pore-Refiner-70-Pads-Salic%C3%ADlico/dp/B0HF61NDMW/ref=sr_1_6?dib=eyJ2IjoiMSJ9.uk1ZaTmLSkCjr1WlUdPnIzLaofEGDgJh9R7zYgwkefy9LuyQiFzUUu0aJIX1BYlx5-wRmSwJSUBKJnX-zzS0X0-VmfHtQQ82JcgAgtGQVEnj9-HHDeyGf3d1rYulXi7i_Ow8QIWh3kQqL7Ll0TijZfSoZQDQadHr_-rf6DfesXMmMibB6sDX6vWc2RnP-foaqCDGyT4duklJcGFpv1u51qTNZl50udCB94NihMSqwrPPI0LzQRiYV6gMXcGuIyLA-BMEaK8C7Ww9vfUFU3IpgOYQ1941MisZvR5CXyW4ppQ.78jHfHg1CNr1xN0-5kzhzBvDSAbiluwmUGIf3gB8a_0&amp;dib_tag=se&amp;keywords=creamy+pore+refiner&amp;qid=1791501119&amp;sr=8-6&amp;ufe=app_do%3Aamzn1.fos.6a09f7ec-d911-4889-ad70-de8dd83c8a74</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46309.89402777778</v>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Celular Samsung Galaxy S26 Ultra 5G, 256GB, 12GB RAM,...</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Mercado Livre</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>7498.89</v>
+      </c>
+      <c r="E142" t="n">
+        <v>6800</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0</v>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>😐 Sem queda</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>JSON-LD</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>https://www.mercadolivre.com.br/celular-samsung-galaxy-s26-ultra-5g-256gb-12gb-ram-camera-quadrupla-tela-grande-de-69-violeta/p/MLB65503990</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46309.89582175926</v>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Headset Razer BlackShark V2 X</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>KaBuM!</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>359.99</v>
+      </c>
+      <c r="E143" t="n">
+        <v>365</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0</v>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>🎯 Meta atingida</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>JSON-LD</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>https://www.kabum.com.br/produto/128544/headset-gamer-razer-blackshark-v2-x-drivers-50mm-microfone-cardioide-surround-7-1-3-5-mm-preto-rz04-03240100</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="n">
+        <v>46309.89589120371</v>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Creme Skincare com Ácido Salicílico | Creamy</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>132.04</v>
+      </c>
+      <c r="E144" t="n">
+        <v>140</v>
+      </c>
+      <c r="F144" t="n">
+        <v>0</v>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>🎯 Meta atingida</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>https://www.amazon.com.br/Pore-Refiner-70-Pads-Salic%C3%ADlico/dp/B0HF61NDMW/ref=sr_1_6?dib=eyJ2IjoiMSJ9.uk1ZaTmLSkCjr1WlUdPnIzLaofEGDgJh9R7zYgwkefy9LuyQiFzUUu0aJIX1BYlx5-wRmSwJSUBKJnX-zzS0X0-VmfHtQQ82JcgAgtGQVEnj9-HHDeyGf3d1rYulXi7i_Ow8QIWh3kQqL7Ll0TijZfSoZQDQadHr_-rf6DfesXMmMibB6sDX6vWc2RnP-foaqCDGyT4duklJcGFpv1u51qTNZl50udCB94NihMSqwrPPI0LzQRiYV6gMXcGuIyLA-BMEaK8C7Ww9vfUFU3IpgOYQ1941MisZvR5CXyW4ppQ.78jHfHg1CNr1xN0-5kzhzBvDSAbiluwmUGIf3gB8a_0&amp;dib_tag=se&amp;keywords=creamy+pore+refiner&amp;qid=1791501119&amp;sr=8-6&amp;ufe=app_do%3Aamzn1.fos.6a09f7ec-d911-4889-ad70-de8dd83c8a74</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="n">
+        <v>46309.89599537037</v>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Celular Samsung Galaxy S26 Ultra 5G, 256GB, 12GB RAM,...</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Mercado Livre</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>7498.89</v>
+      </c>
+      <c r="E145" t="n">
+        <v>6800</v>
+      </c>
+      <c r="F145" t="n">
+        <v>0</v>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>😐 Sem queda</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>JSON-LD</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>https://www.mercadolivre.com.br/celular-samsung-galaxy-s26-ultra-5g-256gb-12gb-ram-camera-quadrupla-tela-grande-de-69-violeta/p/MLB65503990</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="n">
+        <v>46309.89666666667</v>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Headset Razer BlackShark V2 X</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>KaBuM!</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr"/>
+      <c r="E146" t="n">
+        <v>365</v>
+      </c>
+      <c r="F146" t="inlineStr"/>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>❌ Erro</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr"/>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>https://www.kabum.com.br/produto/128544/headset-gamer-razer-blackshark-v2-x-drivers-50mm-microfone-cardioide-surround-7-1-3-5-mm-preto-rz04-03240100</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="n">
+        <v>46309.89666666667</v>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Creme Skincare com Ácido Salicílico | Creamy</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr"/>
+      <c r="E147" t="n">
+        <v>140</v>
+      </c>
+      <c r="F147" t="inlineStr"/>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>❌ Erro</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr"/>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>https://www.amazon.com.br/Pore-Refiner-70-Pads-Salic%C3%ADlico/dp/B0HF61NDMW/ref=sr_1_6?dib=eyJ2IjoiMSJ9.uk1ZaTmLSkCjr1WlUdPnIzLaofEGDgJh9R7zYgwkefy9LuyQiFzUUu0aJIX1BYlx5-wRmSwJSUBKJnX-zzS0X0-VmfHtQQ82JcgAgtGQVEnj9-HHDeyGf3d1rYulXi7i_Ow8QIWh3kQqL7Ll0TijZfSoZQDQadHr_-rf6DfesXMmMibB6sDX6vWc2RnP-foaqCDGyT4duklJcGFpv1u51qTNZl50udCB94NihMSqwrPPI0LzQRiYV6gMXcGuIyLA-BMEaK8C7Ww9vfUFU3IpgOYQ1941MisZvR5CXyW4ppQ.78jHfHg1CNr1xN0-5kzhzBvDSAbiluwmUGIf3gB8a_0&amp;dib_tag=se&amp;keywords=creamy+pore+refiner&amp;qid=1791501119&amp;sr=8-6&amp;ufe=app_do%3Aamzn1.fos.6a09f7ec-d911-4889-ad70-de8dd83c8a74</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="n">
+        <v>46309.89667824074</v>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Celular Samsung Galaxy S26 Ultra 5G, 256GB, 12GB RAM,...</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Mercado Livre</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr"/>
+      <c r="E148" t="n">
+        <v>6800</v>
+      </c>
+      <c r="F148" t="inlineStr"/>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>❌ Erro</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr"/>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>https://www.mercadolivre.com.br/celular-samsung-galaxy-s26-ultra-5g-256gb-12gb-ram-camera-quadrupla-tela-grande-de-69-violeta/p/MLB65503990</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="n">
+        <v>46309.89740740741</v>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Headset Razer BlackShark V2 X</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>KaBuM!</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>359.99</v>
+      </c>
+      <c r="E149" t="n">
+        <v>365</v>
+      </c>
+      <c r="F149" t="n">
+        <v>0</v>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>🎯 Meta atingida</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>JSON-LD</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>https://www.kabum.com.br/produto/128544/headset-gamer-razer-blackshark-v2-x-drivers-50mm-microfone-cardioide-surround-7-1-3-5-mm-preto-rz04-03240100</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="n">
+        <v>46309.89747685185</v>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Creme Skincare com Ácido Salicílico | Creamy</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>132.04</v>
+      </c>
+      <c r="E150" t="n">
+        <v>140</v>
+      </c>
+      <c r="F150" t="n">
+        <v>0</v>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>🎯 Meta atingida</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>https://www.amazon.com.br/Pore-Refiner-70-Pads-Salic%C3%ADlico/dp/B0HF61NDMW/ref=sr_1_6?dib=eyJ2IjoiMSJ9.uk1ZaTmLSkCjr1WlUdPnIzLaofEGDgJh9R7zYgwkefy9LuyQiFzUUu0aJIX1BYlx5-wRmSwJSUBKJnX-zzS0X0-VmfHtQQ82JcgAgtGQVEnj9-HHDeyGf3d1rYulXi7i_Ow8QIWh3kQqL7Ll0TijZfSoZQDQadHr_-rf6DfesXMmMibB6sDX6vWc2RnP-foaqCDGyT4duklJcGFpv1u51qTNZl50udCB94NihMSqwrPPI0LzQRiYV6gMXcGuIyLA-BMEaK8C7Ww9vfUFU3IpgOYQ1941MisZvR5CXyW4ppQ.78jHfHg1CNr1xN0-5kzhzBvDSAbiluwmUGIf3gB8a_0&amp;dib_tag=se&amp;keywords=creamy+pore+refiner&amp;qid=1791501119&amp;sr=8-6&amp;ufe=app_do%3Aamzn1.fos.6a09f7ec-d911-4889-ad70-de8dd83c8a74</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="n">
+        <v>46309.89756944445</v>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Celular Samsung Galaxy S26 Ultra 5G, 256GB, 12GB RAM,...</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Mercado Livre</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>7498.89</v>
+      </c>
+      <c r="E151" t="n">
+        <v>6800</v>
+      </c>
+      <c r="F151" t="n">
+        <v>0</v>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>😐 Sem queda</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>JSON-LD</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>https://www.mercadolivre.com.br/celular-samsung-galaxy-s26-ultra-5g-256gb-12gb-ram-camera-quadrupla-tela-grande-de-69-violeta/p/MLB65503990</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="n">
+        <v>46309.89903935185</v>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Headset Razer BlackShark V2 X</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>KaBuM!</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>359.99</v>
+      </c>
+      <c r="E152" t="n">
+        <v>365</v>
+      </c>
+      <c r="F152" t="n">
+        <v>0</v>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>🎯 Meta atingida</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>JSON-LD</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>https://www.kabum.com.br/produto/128544/headset-gamer-razer-blackshark-v2-x-drivers-50mm-microfone-cardioide-surround-7-1-3-5-mm-preto-rz04-03240100</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="n">
+        <v>46309.89907407408</v>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Creme Skincare com Ácido Salicílico | Creamy</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>132.04</v>
+      </c>
+      <c r="E153" t="n">
+        <v>140</v>
+      </c>
+      <c r="F153" t="n">
+        <v>0</v>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>🎯 Meta atingida</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>https://www.amazon.com.br/Pore-Refiner-70-Pads-Salic%C3%ADlico/dp/B0HF61NDMW/ref=sr_1_6?dib=eyJ2IjoiMSJ9.uk1ZaTmLSkCjr1WlUdPnIzLaofEGDgJh9R7zYgwkefy9LuyQiFzUUu0aJIX1BYlx5-wRmSwJSUBKJnX-zzS0X0-VmfHtQQ82JcgAgtGQVEnj9-HHDeyGf3d1rYulXi7i_Ow8QIWh3kQqL7Ll0TijZfSoZQDQadHr_-rf6DfesXMmMibB6sDX6vWc2RnP-foaqCDGyT4duklJcGFpv1u51qTNZl50udCB94NihMSqwrPPI0LzQRiYV6gMXcGuIyLA-BMEaK8C7Ww9vfUFU3IpgOYQ1941MisZvR5CXyW4ppQ.78jHfHg1CNr1xN0-5kzhzBvDSAbiluwmUGIf3gB8a_0&amp;dib_tag=se&amp;keywords=creamy+pore+refiner&amp;qid=1791501119&amp;sr=8-6&amp;ufe=app_do%3Aamzn1.fos.6a09f7ec-d911-4889-ad70-de8dd83c8a74</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="n">
+        <v>46309.89915509259</v>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Celular Samsung Galaxy S26 Ultra 5G, 256GB, 12GB RAM,...</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Mercado Livre</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>7498.89</v>
+      </c>
+      <c r="E154" t="n">
+        <v>6800</v>
+      </c>
+      <c r="F154" t="n">
+        <v>0</v>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>😐 Sem queda</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>JSON-LD</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>https://www.mercadolivre.com.br/celular-samsung-galaxy-s26-ultra-5g-256gb-12gb-ram-camera-quadrupla-tela-grande-de-69-violeta/p/MLB65503990</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="n">
+        <v>46309.89950231482</v>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Headset Razer BlackShark V2 X</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>KaBuM!</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>359.99</v>
+      </c>
+      <c r="E155" t="n">
+        <v>365</v>
+      </c>
+      <c r="F155" t="n">
+        <v>0</v>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>🎯 Meta atingida</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>JSON-LD</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>https://www.kabum.com.br/produto/128544/headset-gamer-razer-blackshark-v2-x-drivers-50mm-microfone-cardioide-surround-7-1-3-5-mm-preto-rz04-03240100</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="n">
+        <v>46309.89954861111</v>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Creme Skincare com Ácido Salicílico | Creamy</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="D156" t="n">
+        <v>132.04</v>
+      </c>
+      <c r="E156" t="n">
+        <v>140</v>
+      </c>
+      <c r="F156" t="n">
+        <v>0</v>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>🎯 Meta atingida</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>https://www.amazon.com.br/Pore-Refiner-70-Pads-Salic%C3%ADlico/dp/B0HF61NDMW/ref=sr_1_6?dib=eyJ2IjoiMSJ9.uk1ZaTmLSkCjr1WlUdPnIzLaofEGDgJh9R7zYgwkefy9LuyQiFzUUu0aJIX1BYlx5-wRmSwJSUBKJnX-zzS0X0-VmfHtQQ82JcgAgtGQVEnj9-HHDeyGf3d1rYulXi7i_Ow8QIWh3kQqL7Ll0TijZfSoZQDQadHr_-rf6DfesXMmMibB6sDX6vWc2RnP-foaqCDGyT4duklJcGFpv1u51qTNZl50udCB94NihMSqwrPPI0LzQRiYV6gMXcGuIyLA-BMEaK8C7Ww9vfUFU3IpgOYQ1941MisZvR5CXyW4ppQ.78jHfHg1CNr1xN0-5kzhzBvDSAbiluwmUGIf3gB8a_0&amp;dib_tag=se&amp;keywords=creamy+pore+refiner&amp;qid=1791501119&amp;sr=8-6&amp;ufe=app_do%3Aamzn1.fos.6a09f7ec-d911-4889-ad70-de8dd83c8a74</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="n">
+        <v>46309.8996412037</v>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Celular Samsung Galaxy S26 Ultra 5G, 256GB, 12GB RAM,...</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Mercado Livre</t>
+        </is>
+      </c>
+      <c r="D157" t="n">
+        <v>7498.89</v>
+      </c>
+      <c r="E157" t="n">
+        <v>6800</v>
+      </c>
+      <c r="F157" t="n">
+        <v>0</v>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>😐 Sem queda</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>JSON-LD</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>https://www.mercadolivre.com.br/celular-samsung-galaxy-s26-ultra-5g-256gb-12gb-ram-camera-quadrupla-tela-grande-de-69-violeta/p/MLB65503990</t>
         </is>
       </c>
     </row>
